--- a/poi_prepared_data.xlsx
+++ b/poi_prepared_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,65 +436,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>HOTEL_CITY</t>
+          <t>HOTEL_LAT</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>HOTEL_LAT</t>
+          <t>HOTEL_LON</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>HOTEL_LON</t>
+          <t>fb_0_1km</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>fb_0_1km</t>
+          <t>fb_0_2km</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>fb_0_2km</t>
+          <t>fb_0_3km</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fb_0_3km</t>
+          <t>fb_0_4km</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>fb_0_4km</t>
+          <t>fb_0_5km</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>fb_0_5km</t>
+          <t>not_fb_0_1km</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>not_fb_0_1km</t>
+          <t>not_fb_0_2km</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>not_fb_0_2km</t>
+          <t>not_fb_0_3km</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>not_fb_0_3km</t>
+          <t>not_fb_0_4km</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>not_fb_0_4km</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>not_fb_0_5km</t>
         </is>
@@ -506,16 +501,14 @@
           <t>Ibis budget Nice</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
+      <c r="B2" t="n">
+        <v>43.6675713</v>
       </c>
       <c r="C2" t="n">
-        <v>43.6675713</v>
+        <v>7.2143076</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2143076</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -524,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -536,15 +529,12 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -554,45 +544,40 @@
           <t>Ibis budget Strasbourg Centre République</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
+      <c r="B3" t="n">
+        <v>48.5850581</v>
       </c>
       <c r="C3" t="n">
-        <v>48.5850581</v>
+        <v>7.7365913</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7365913</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H3" t="n">
-        <v>102</v>
-      </c>
-      <c r="I3" t="n">
-        <v>120</v>
-      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
-      </c>
-      <c r="N3" t="n">
         <v>36</v>
       </c>
     </row>
@@ -602,45 +587,40 @@
           <t>Mercure Paris Montmartre Sacré-Cœur</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
+      <c r="B4" t="n">
+        <v>48.8852398</v>
       </c>
       <c r="C4" t="n">
-        <v>48.8852398</v>
+        <v>2.3300554</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3300554</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="H4" t="n">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="I4" t="n">
-        <v>195</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
-      </c>
-      <c r="N4" t="n">
         <v>54</v>
       </c>
     </row>
@@ -650,45 +630,40 @@
           <t>Novotel Megève Mont-Blanc</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Megève</t>
-        </is>
+      <c r="B5" t="n">
+        <v>45.8598495</v>
       </c>
       <c r="C5" t="n">
-        <v>45.8598495</v>
+        <v>6.6194782</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6194782</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -698,45 +673,40 @@
           <t>Novotel Paris Tour Eiffel</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
+      <c r="B6" t="n">
+        <v>48.8496595</v>
       </c>
       <c r="C6" t="n">
-        <v>48.8496595</v>
+        <v>2.2837039</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2837039</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>69</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="n">
-        <v>36</v>
-      </c>
-      <c r="I6" t="n">
-        <v>69</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
-      </c>
-      <c r="N6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -746,31 +716,29 @@
           <t>Novotel Porte d’Italie</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
+      <c r="B7" t="n">
+        <v>48.819054</v>
       </c>
       <c r="C7" t="n">
-        <v>48.819054</v>
+        <v>2.3594056</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3594056</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I7" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -779,12 +747,9 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" t="n">
         <v>9</v>
       </c>
     </row>
